--- a/BESS_optimiser/output/Result.xlsx
+++ b/BESS_optimiser/output/Result.xlsx
@@ -41,292 +41,292 @@
     <t>Charge Status</t>
   </si>
   <si>
-    <t>28/09/2024 02:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 02:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 02:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 02:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 03:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 03:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 03:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 03:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 04:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 04:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 04:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 04:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 05:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 05:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 05:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 05:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 06:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 06:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 06:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 06:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 07:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 07:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 07:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 07:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 08:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 08:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 08:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 08:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 09:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 09:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 09:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 09:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 10:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 10:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 10:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 10:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 11:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 11:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 11:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 11:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 12:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 12:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 12:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 12:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 13:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 13:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 13:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 13:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 14:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 14:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 14:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 14:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 15:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 15:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 15:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 15:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 16:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 16:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 16:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 16:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 17:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 17:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 17:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 17:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 18:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 18:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 18:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 18:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 19:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 19:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 19:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 19:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 20:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 20:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 20:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 20:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 21:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 21:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 21:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 21:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 22:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 22:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 22:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 22:45</t>
-  </si>
-  <si>
-    <t>28/09/2024 23:00</t>
-  </si>
-  <si>
-    <t>28/09/2024 23:15</t>
-  </si>
-  <si>
-    <t>28/09/2024 23:30</t>
-  </si>
-  <si>
-    <t>28/09/2024 23:45</t>
-  </si>
-  <si>
-    <t>29/09/2024 00:00</t>
-  </si>
-  <si>
-    <t>29/09/2024 00:15</t>
-  </si>
-  <si>
-    <t>29/09/2024 00:30</t>
-  </si>
-  <si>
-    <t>29/09/2024 00:45</t>
-  </si>
-  <si>
-    <t>29/09/2024 01:00</t>
-  </si>
-  <si>
-    <t>29/09/2024 01:15</t>
-  </si>
-  <si>
-    <t>29/09/2024 01:30</t>
-  </si>
-  <si>
-    <t>29/09/2024 01:45</t>
+    <t>25/10/2024 01:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 01:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 01:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 01:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 02:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 02:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 02:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 02:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 03:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 03:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 03:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 03:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 04:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 04:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 04:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 04:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 05:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 05:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 05:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 05:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 06:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 06:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 06:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 06:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 07:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 07:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 07:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 07:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 08:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 08:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 08:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 08:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 09:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 09:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 09:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 09:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 10:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 10:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 10:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 10:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 11:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 11:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 11:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 11:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 12:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 12:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 12:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 12:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 13:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 13:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 13:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 13:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 14:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 14:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 14:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 14:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 15:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 15:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 15:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 15:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 16:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 16:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 16:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 16:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 17:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 17:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 17:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 17:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 18:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 18:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 18:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 18:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 19:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 19:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 19:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 19:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 20:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 20:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 20:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 20:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 21:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 21:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 21:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 21:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 22:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 22:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 22:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 22:45</t>
+  </si>
+  <si>
+    <t>25/10/2024 23:00</t>
+  </si>
+  <si>
+    <t>25/10/2024 23:15</t>
+  </si>
+  <si>
+    <t>25/10/2024 23:30</t>
+  </si>
+  <si>
+    <t>25/10/2024 23:45</t>
+  </si>
+  <si>
+    <t>26/10/2024 00:00</t>
+  </si>
+  <si>
+    <t>26/10/2024 00:15</t>
+  </si>
+  <si>
+    <t>26/10/2024 00:30</t>
+  </si>
+  <si>
+    <t>26/10/2024 00:45</t>
   </si>
 </sst>
 </file>
@@ -697,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>48305.16</v>
+        <v>28489.78</v>
       </c>
     </row>
   </sheetData>
@@ -735,7 +735,7 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>2048</v>
+        <v>7667.5</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>2287</v>
+        <v>7656.25</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -781,7 +781,7 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>2508.75</v>
+        <v>7640.25</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>2578.25</v>
+        <v>7628.25</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -827,7 +827,7 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>4163.1974</v>
+        <v>9203.447399999999</v>
       </c>
       <c r="C6">
         <v>-1578.9474</v>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>4617.25</v>
+        <v>9681.75</v>
       </c>
       <c r="C7">
         <v>-2000</v>
@@ -873,7 +873,7 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>4681.25</v>
+        <v>9710</v>
       </c>
       <c r="C8">
         <v>-2000</v>
@@ -896,7 +896,7 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>4724.75</v>
+        <v>9673</v>
       </c>
       <c r="C9">
         <v>-2000</v>
@@ -919,7 +919,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>2804</v>
+        <v>7619.75</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>3014.75</v>
+        <v>7663.5</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -965,7 +965,7 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>3241</v>
+        <v>7791.75</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>3358.25</v>
+        <v>7888.75</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>3590.25</v>
+        <v>8036</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1034,7 +1034,7 @@
         <v>21</v>
       </c>
       <c r="B15">
-        <v>3693.25</v>
+        <v>8109.25</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1057,7 +1057,7 @@
         <v>22</v>
       </c>
       <c r="B16">
-        <v>3755.5</v>
+        <v>8196.5</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>23</v>
       </c>
       <c r="B17">
-        <v>3891</v>
+        <v>8316</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1103,7 +1103,7 @@
         <v>24</v>
       </c>
       <c r="B18">
-        <v>4048.25</v>
+        <v>8560.25</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1126,7 +1126,7 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>4296.75</v>
+        <v>8714.25</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>4450.25</v>
+        <v>8937.5</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1172,7 +1172,7 @@
         <v>27</v>
       </c>
       <c r="B21">
-        <v>4638.75</v>
+        <v>9264.75</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1187,7 +1187,7 @@
         <v>0.95</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1195,19 +1195,19 @@
         <v>28</v>
       </c>
       <c r="B22">
-        <v>2914.75</v>
+        <v>9931.25</v>
       </c>
       <c r="C22">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>0.8184</v>
+        <v>0.95</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1218,19 +1218,19 @@
         <v>29</v>
       </c>
       <c r="B23">
-        <v>4119.25</v>
+        <v>10349.75</v>
       </c>
       <c r="C23">
-        <v>920</v>
+        <v>-0</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>920</v>
+        <v>-0</v>
       </c>
       <c r="F23">
-        <v>0.7579</v>
+        <v>0.95</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1241,19 +1241,19 @@
         <v>30</v>
       </c>
       <c r="B24">
-        <v>3149</v>
+        <v>10686.75</v>
       </c>
       <c r="C24">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>0.6263</v>
+        <v>0.95</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>5430</v>
+        <v>11046.75</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1276,10 +1276,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0.6263</v>
+        <v>0.95</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1287,19 +1287,19 @@
         <v>32</v>
       </c>
       <c r="B26">
-        <v>3649.25</v>
+        <v>10514.5</v>
       </c>
       <c r="C26">
-        <v>2000</v>
+        <v>920</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>2000</v>
+        <v>920</v>
       </c>
       <c r="F26">
-        <v>0.4947</v>
+        <v>0.8895</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1310,7 +1310,7 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <v>3565.75</v>
+        <v>9706.75</v>
       </c>
       <c r="C27">
         <v>2000</v>
@@ -1322,7 +1322,7 @@
         <v>2000</v>
       </c>
       <c r="F27">
-        <v>0.3632</v>
+        <v>0.7579</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1333,7 +1333,7 @@
         <v>34</v>
       </c>
       <c r="B28">
-        <v>3487.5</v>
+        <v>10016</v>
       </c>
       <c r="C28">
         <v>2000</v>
@@ -1345,7 +1345,7 @@
         <v>2000</v>
       </c>
       <c r="F28">
-        <v>0.2316</v>
+        <v>0.6263</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -1356,19 +1356,19 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>3393.75</v>
+        <v>12225.25</v>
       </c>
       <c r="C29">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>0.1</v>
+        <v>0.6263</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1379,19 +1379,19 @@
         <v>36</v>
       </c>
       <c r="B30">
-        <v>5156.75</v>
+        <v>10366.75</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F30">
-        <v>0.1</v>
+        <v>0.4947</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1402,19 +1402,19 @@
         <v>37</v>
       </c>
       <c r="B31">
-        <v>4938.75</v>
+        <v>10377.5</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F31">
-        <v>0.1</v>
+        <v>0.3632</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -1425,19 +1425,19 @@
         <v>38</v>
       </c>
       <c r="B32">
-        <v>4776.25</v>
+        <v>10274.5</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F32">
-        <v>0.1</v>
+        <v>0.2316</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>4440.75</v>
+        <v>10102</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F33">
         <v>0.1</v>
@@ -1471,7 +1471,7 @@
         <v>40</v>
       </c>
       <c r="B34">
-        <v>3802</v>
+        <v>11811.5</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>41</v>
       </c>
       <c r="B35">
-        <v>3296.75</v>
+        <v>11628.25</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1517,7 +1517,7 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>2894.5</v>
+        <v>11356.5</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1540,7 +1540,7 @@
         <v>43</v>
       </c>
       <c r="B37">
-        <v>2665.5</v>
+        <v>11077.25</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -1555,7 +1555,7 @@
         <v>0.1</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1563,7 +1563,7 @@
         <v>44</v>
       </c>
       <c r="B38">
-        <v>2333</v>
+        <v>10791.25</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>45</v>
       </c>
       <c r="B39">
-        <v>2005</v>
+        <v>10565.75</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1609,7 +1609,7 @@
         <v>46</v>
       </c>
       <c r="B40">
-        <v>1921.25</v>
+        <v>10405.75</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>47</v>
       </c>
       <c r="B41">
-        <v>1944.5</v>
+        <v>10186.25</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -1655,7 +1655,7 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>1543.5</v>
+        <v>9930.25</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>49</v>
       </c>
       <c r="B43">
-        <v>1225.5</v>
+        <v>9657.25</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>50</v>
       </c>
       <c r="B44">
-        <v>1217.25</v>
+        <v>9417.75</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0.1</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1724,7 +1724,7 @@
         <v>51</v>
       </c>
       <c r="B45">
-        <v>1386.75</v>
+        <v>9238</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>52</v>
       </c>
       <c r="B46">
-        <v>3122.75</v>
+        <v>10958.5</v>
       </c>
       <c r="C46">
         <v>-2000</v>
@@ -1770,19 +1770,19 @@
         <v>53</v>
       </c>
       <c r="B47">
-        <v>2881.25</v>
+        <v>8969.789500000001</v>
       </c>
       <c r="C47">
-        <v>-2000</v>
+        <v>-315.7895</v>
       </c>
       <c r="D47">
-        <v>-2000</v>
+        <v>-315.7895</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>0.3375</v>
+        <v>0.2375</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -1793,7 +1793,7 @@
         <v>54</v>
       </c>
       <c r="B48">
-        <v>3111.25</v>
+        <v>10431</v>
       </c>
       <c r="C48">
         <v>-2000</v>
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>0.4563</v>
+        <v>0.3562</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -1816,7 +1816,7 @@
         <v>55</v>
       </c>
       <c r="B49">
-        <v>3014</v>
+        <v>10247</v>
       </c>
       <c r="C49">
         <v>-2000</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>0.575</v>
+        <v>0.475</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -1839,7 +1839,7 @@
         <v>56</v>
       </c>
       <c r="B50">
-        <v>3107</v>
+        <v>10149</v>
       </c>
       <c r="C50">
         <v>-2000</v>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>0.6938</v>
+        <v>0.5938</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -1862,7 +1862,7 @@
         <v>57</v>
       </c>
       <c r="B51">
-        <v>3293.5</v>
+        <v>10112.5</v>
       </c>
       <c r="C51">
         <v>-2000</v>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>0.8125</v>
+        <v>0.7125</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -1885,7 +1885,7 @@
         <v>58</v>
       </c>
       <c r="B52">
-        <v>3309.75</v>
+        <v>10044.75</v>
       </c>
       <c r="C52">
         <v>-2000</v>
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>0.9313</v>
+        <v>0.8312</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -1908,13 +1908,13 @@
         <v>59</v>
       </c>
       <c r="B53">
-        <v>1784.0395</v>
+        <v>9909.75</v>
       </c>
       <c r="C53">
-        <v>-315.7895</v>
+        <v>-2000</v>
       </c>
       <c r="D53">
-        <v>-315.7895</v>
+        <v>-2000</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1931,7 +1931,7 @@
         <v>60</v>
       </c>
       <c r="B54">
-        <v>1683.25</v>
+        <v>7937</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>61</v>
       </c>
       <c r="B55">
-        <v>1569</v>
+        <v>7984.25</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1977,7 +1977,7 @@
         <v>62</v>
       </c>
       <c r="B56">
-        <v>1884.5</v>
+        <v>8071.5</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>63</v>
       </c>
       <c r="B57">
-        <v>2117.5</v>
+        <v>8251.25</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         <v>64</v>
       </c>
       <c r="B58">
-        <v>2291.75</v>
+        <v>8461</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>65</v>
       </c>
       <c r="B59">
-        <v>2392</v>
+        <v>8680.75</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -2069,7 +2069,7 @@
         <v>66</v>
       </c>
       <c r="B60">
-        <v>2689</v>
+        <v>9011.75</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2092,7 +2092,7 @@
         <v>67</v>
       </c>
       <c r="B61">
-        <v>3359</v>
+        <v>9408.25</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2115,7 +2115,7 @@
         <v>68</v>
       </c>
       <c r="B62">
-        <v>4428.75</v>
+        <v>9962</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>69</v>
       </c>
       <c r="B63">
-        <v>5039</v>
+        <v>10403.75</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2161,7 +2161,7 @@
         <v>70</v>
       </c>
       <c r="B64">
-        <v>5535.5</v>
+        <v>10948</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2184,7 +2184,7 @@
         <v>71</v>
       </c>
       <c r="B65">
-        <v>6260.25</v>
+        <v>11532.5</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2207,7 +2207,7 @@
         <v>72</v>
       </c>
       <c r="B66">
-        <v>6902.5</v>
+        <v>12113</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2230,16 +2230,16 @@
         <v>73</v>
       </c>
       <c r="B67">
-        <v>7348</v>
+        <v>12566.5</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F67">
         <v>0.95</v>
@@ -2253,7 +2253,7 @@
         <v>74</v>
       </c>
       <c r="B68">
-        <v>7668.5</v>
+        <v>13029.25</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>75</v>
       </c>
       <c r="B69">
-        <v>7832</v>
+        <v>13289.5</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>76</v>
       </c>
       <c r="B70">
-        <v>6032.25</v>
+        <v>11389.75</v>
       </c>
       <c r="C70">
         <v>2000</v>
@@ -2322,7 +2322,7 @@
         <v>77</v>
       </c>
       <c r="B71">
-        <v>6231.25</v>
+        <v>11603</v>
       </c>
       <c r="C71">
         <v>2000</v>
@@ -2345,7 +2345,7 @@
         <v>78</v>
       </c>
       <c r="B72">
-        <v>6270.25</v>
+        <v>11697</v>
       </c>
       <c r="C72">
         <v>2000</v>
@@ -2368,7 +2368,7 @@
         <v>79</v>
       </c>
       <c r="B73">
-        <v>6194.25</v>
+        <v>11702.25</v>
       </c>
       <c r="C73">
         <v>2000</v>
@@ -2391,7 +2391,7 @@
         <v>80</v>
       </c>
       <c r="B74">
-        <v>6043</v>
+        <v>11478</v>
       </c>
       <c r="C74">
         <v>2000</v>
@@ -2414,7 +2414,7 @@
         <v>81</v>
       </c>
       <c r="B75">
-        <v>7874.5</v>
+        <v>13303.75</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>82</v>
       </c>
       <c r="B76">
-        <v>5752</v>
+        <v>11147.75</v>
       </c>
       <c r="C76">
         <v>2000</v>
@@ -2460,7 +2460,7 @@
         <v>83</v>
       </c>
       <c r="B77">
-        <v>6659.75</v>
+        <v>12023</v>
       </c>
       <c r="C77">
         <v>920</v>
@@ -2483,7 +2483,7 @@
         <v>84</v>
       </c>
       <c r="B78">
-        <v>7300.75</v>
+        <v>12648.5</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2506,7 +2506,7 @@
         <v>85</v>
       </c>
       <c r="B79">
-        <v>7140.5</v>
+        <v>12351.25</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2529,7 +2529,7 @@
         <v>86</v>
       </c>
       <c r="B80">
-        <v>7109.5</v>
+        <v>12107</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2552,7 +2552,7 @@
         <v>87</v>
       </c>
       <c r="B81">
-        <v>7022.75</v>
+        <v>11876.5</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>88</v>
       </c>
       <c r="B82">
-        <v>6995.25</v>
+        <v>11747.75</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>89</v>
       </c>
       <c r="B83">
-        <v>6751</v>
+        <v>11478.25</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>90</v>
       </c>
       <c r="B84">
-        <v>6565.5</v>
+        <v>11357</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2644,7 +2644,7 @@
         <v>91</v>
       </c>
       <c r="B85">
-        <v>6466</v>
+        <v>11147</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>92</v>
       </c>
       <c r="B86">
-        <v>6313</v>
+        <v>10979.5</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>93</v>
       </c>
       <c r="B87">
-        <v>6408.25</v>
+        <v>10749.25</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2713,7 +2713,7 @@
         <v>94</v>
       </c>
       <c r="B88">
-        <v>6429.25</v>
+        <v>10607</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>95</v>
       </c>
       <c r="B89">
-        <v>6206.5</v>
+        <v>10349.75</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>96</v>
       </c>
       <c r="B90">
-        <v>5886.25</v>
+        <v>10160.75</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2782,7 +2782,7 @@
         <v>97</v>
       </c>
       <c r="B91">
-        <v>5811</v>
+        <v>9970.25</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>98</v>
       </c>
       <c r="B92">
-        <v>5873</v>
+        <v>9757.75</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>99</v>
       </c>
       <c r="B93">
-        <v>5867</v>
+        <v>9575.5</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2851,7 +2851,7 @@
         <v>100</v>
       </c>
       <c r="B94">
-        <v>5877</v>
+        <v>9415.25</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2874,7 +2874,7 @@
         <v>101</v>
       </c>
       <c r="B95">
-        <v>5807</v>
+        <v>9294</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2897,7 +2897,7 @@
         <v>102</v>
       </c>
       <c r="B96">
-        <v>5830.75</v>
+        <v>9221</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2920,7 +2920,7 @@
         <v>103</v>
       </c>
       <c r="B97">
-        <v>5794.5</v>
+        <v>9200.25</v>
       </c>
       <c r="C97">
         <v>0</v>
